--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DFS_HRM-2031-0192/panel_11/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DFS_HRM-2031-0192/panel_11/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,26 +456,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>Pad Pos 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.88146</v>
+        <v>16.87445</v>
       </c>
       <c r="D2" t="n">
-        <v>16.62533</v>
+        <v>16.78336</v>
       </c>
       <c r="E2" t="n">
-        <v>17.09272</v>
+        <v>16.7971</v>
       </c>
       <c r="F2" t="n">
-        <v>42.86621</v>
+        <v>42.67384</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05109</v>
+        <v>0.05147</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8489</v>
+        <v>1.79736</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.0048</v>
+        <v>17.0355</v>
       </c>
       <c r="D3" t="n">
-        <v>16.50438</v>
+        <v>16.56879</v>
       </c>
       <c r="E3" t="n">
-        <v>17.28569</v>
+        <v>16.95378</v>
       </c>
       <c r="F3" t="n">
-        <v>42.97456</v>
+        <v>43.07562</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0518</v>
+        <v>0.05023</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7928</v>
+        <v>1.8001</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.94462</v>
+        <v>17.07271</v>
       </c>
       <c r="D4" t="n">
-        <v>16.55495</v>
+        <v>16.84093</v>
       </c>
       <c r="E4" t="n">
-        <v>16.86038</v>
+        <v>16.95005</v>
       </c>
       <c r="F4" t="n">
-        <v>42.61973</v>
+        <v>42.36114</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05299</v>
+        <v>0.05129</v>
       </c>
       <c r="H4" t="n">
-        <v>1.87567</v>
+        <v>1.85928</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.02115</v>
+        <v>17.01862</v>
       </c>
       <c r="D5" t="n">
-        <v>16.76828</v>
+        <v>16.69412</v>
       </c>
       <c r="E5" t="n">
-        <v>16.97381</v>
+        <v>16.86174</v>
       </c>
       <c r="F5" t="n">
-        <v>42.9766</v>
+        <v>43.17288</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05187</v>
+        <v>0.0506</v>
       </c>
       <c r="H5" t="n">
-        <v>1.85781</v>
+        <v>1.81008</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.90388</v>
+        <v>17.07515</v>
       </c>
       <c r="D6" t="n">
-        <v>16.88317</v>
+        <v>16.56799</v>
       </c>
       <c r="E6" t="n">
-        <v>16.64124</v>
+        <v>16.72664</v>
       </c>
       <c r="F6" t="n">
-        <v>43.51542</v>
+        <v>43.49333</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05135</v>
+        <v>0.05077</v>
       </c>
       <c r="H6" t="n">
-        <v>1.85917</v>
+        <v>1.81615</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.82679</v>
+        <v>16.95798</v>
       </c>
       <c r="D7" t="n">
-        <v>16.80265</v>
+        <v>16.55989</v>
       </c>
       <c r="E7" t="n">
-        <v>16.76015</v>
+        <v>16.77216</v>
       </c>
       <c r="F7" t="n">
-        <v>42.53384</v>
+        <v>43.54419</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05142</v>
+        <v>0.05255</v>
       </c>
       <c r="H7" t="n">
-        <v>1.83532</v>
+        <v>1.82621</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.14722</v>
+        <v>17.18246</v>
       </c>
       <c r="D8" t="n">
-        <v>16.42654</v>
+        <v>16.58602</v>
       </c>
       <c r="E8" t="n">
-        <v>16.84809</v>
+        <v>17.05797</v>
       </c>
       <c r="F8" t="n">
-        <v>43.4199</v>
+        <v>43.66125</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05156</v>
+        <v>0.05047</v>
       </c>
       <c r="H8" t="n">
-        <v>1.84459</v>
+        <v>1.88704</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.70205</v>
+        <v>17.11987</v>
       </c>
       <c r="D9" t="n">
-        <v>16.91396</v>
+        <v>16.59413</v>
       </c>
       <c r="E9" t="n">
-        <v>16.6363</v>
+        <v>16.76901</v>
       </c>
       <c r="F9" t="n">
-        <v>43.62091</v>
+        <v>42.42111</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05096</v>
+        <v>0.05127</v>
       </c>
       <c r="H9" t="n">
-        <v>1.82583</v>
+        <v>1.86692</v>
       </c>
     </row>
     <row r="10">
@@ -660,386 +660,1044 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.77697</v>
+        <v>17.00266</v>
       </c>
       <c r="D10" t="n">
-        <v>16.62667</v>
+        <v>16.46178</v>
       </c>
       <c r="E10" t="n">
-        <v>16.97418</v>
+        <v>16.82876</v>
       </c>
       <c r="F10" t="n">
-        <v>42.92647</v>
+        <v>43.54566</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05177</v>
+        <v>0.05061</v>
       </c>
       <c r="H10" t="n">
-        <v>1.84807</v>
+        <v>1.83846</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Pad 2</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>16.80645</v>
-      </c>
-      <c r="D11" t="n">
-        <v>16.90768</v>
-      </c>
-      <c r="E11" t="n">
-        <v>17.24511</v>
-      </c>
-      <c r="F11" t="n">
-        <v>42.36985</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.05084</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.82127</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pad Pos 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.88421</v>
+        <v>17.48244</v>
       </c>
       <c r="D12" t="n">
-        <v>16.62417</v>
+        <v>16.22003</v>
       </c>
       <c r="E12" t="n">
-        <v>16.78904</v>
+        <v>17.36173</v>
       </c>
       <c r="F12" t="n">
-        <v>42.66682</v>
+        <v>44.15323</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05203</v>
+        <v>0.05082</v>
       </c>
       <c r="H12" t="n">
-        <v>1.84555</v>
+        <v>1.85725</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.09996</v>
+        <v>16.85296</v>
       </c>
       <c r="D13" t="n">
-        <v>16.69452</v>
+        <v>16.62181</v>
       </c>
       <c r="E13" t="n">
-        <v>16.63022</v>
+        <v>16.67479</v>
       </c>
       <c r="F13" t="n">
-        <v>42.92667</v>
+        <v>43.34779</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05103</v>
+        <v>0.05065</v>
       </c>
       <c r="H13" t="n">
-        <v>1.85396</v>
+        <v>1.7858</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.58601</v>
+        <v>17.26379</v>
       </c>
       <c r="D14" t="n">
-        <v>16.41395</v>
+        <v>16.5</v>
       </c>
       <c r="E14" t="n">
-        <v>16.84088</v>
+        <v>16.6251</v>
       </c>
       <c r="F14" t="n">
-        <v>42.91315</v>
+        <v>42.38628</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05034</v>
+        <v>0.05075</v>
       </c>
       <c r="H14" t="n">
-        <v>1.84417</v>
+        <v>1.85283</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.94231</v>
+        <v>17.24459</v>
       </c>
       <c r="D15" t="n">
-        <v>16.7267</v>
+        <v>16.79091</v>
       </c>
       <c r="E15" t="n">
-        <v>16.75579</v>
+        <v>17.08843</v>
       </c>
       <c r="F15" t="n">
-        <v>42.87209</v>
+        <v>43.34628</v>
       </c>
       <c r="G15" t="n">
-        <v>0.04954</v>
+        <v>0.05213</v>
       </c>
       <c r="H15" t="n">
-        <v>1.83227</v>
+        <v>1.86357</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.15595</v>
+        <v>17.09666</v>
       </c>
       <c r="D16" t="n">
-        <v>17.04448</v>
+        <v>16.78669</v>
       </c>
       <c r="E16" t="n">
-        <v>17.07048</v>
+        <v>17.01338</v>
       </c>
       <c r="F16" t="n">
-        <v>43.5747</v>
+        <v>43.29147</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05069</v>
+        <v>0.05133</v>
       </c>
       <c r="H16" t="n">
-        <v>1.86245</v>
+        <v>1.84542</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.00848</v>
+        <v>17.08277</v>
       </c>
       <c r="D17" t="n">
-        <v>17.08768</v>
+        <v>16.26289</v>
       </c>
       <c r="E17" t="n">
-        <v>16.83807</v>
+        <v>16.59396</v>
       </c>
       <c r="F17" t="n">
-        <v>44.31643</v>
+        <v>42.78828</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05136</v>
+        <v>0.0506</v>
       </c>
       <c r="H17" t="n">
-        <v>1.81739</v>
+        <v>1.84088</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.95406</v>
+        <v>17.08403</v>
       </c>
       <c r="D18" t="n">
-        <v>16.60449</v>
+        <v>16.79078</v>
       </c>
       <c r="E18" t="n">
-        <v>17.00927</v>
+        <v>16.80744</v>
       </c>
       <c r="F18" t="n">
-        <v>42.81453</v>
+        <v>43.10554</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05052</v>
+        <v>0.05239</v>
       </c>
       <c r="H18" t="n">
-        <v>1.85516</v>
+        <v>1.83136</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>16.81734</v>
+      </c>
+      <c r="D19" t="n">
+        <v>16.67846</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.80804</v>
+      </c>
+      <c r="F19" t="n">
+        <v>43.59525</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.05103</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.83106</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>17.21954</v>
-      </c>
-      <c r="D19" t="n">
-        <v>16.7936</v>
-      </c>
-      <c r="E19" t="n">
-        <v>16.92562</v>
-      </c>
-      <c r="F19" t="n">
-        <v>43.72971</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.0518</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.83723</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="C20" t="n">
+        <v>17.27767</v>
+      </c>
+      <c r="D20" t="n">
+        <v>16.99895</v>
+      </c>
+      <c r="E20" t="n">
+        <v>17.0319</v>
+      </c>
+      <c r="F20" t="n">
+        <v>43.5153</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.05192</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.82602</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>via 1</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0.60802</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1.14434</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SR Pad Pos 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.61758</v>
+        <v>16.04199</v>
       </c>
       <c r="D22" t="n">
-        <v>1.13822</v>
+        <v>15.76594</v>
+      </c>
+      <c r="E22" t="n">
+        <v>15.90749</v>
+      </c>
+      <c r="F22" t="n">
+        <v>259.59651</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.62608</v>
+        <v>16.09026</v>
       </c>
       <c r="D23" t="n">
-        <v>1.12538</v>
+        <v>15.58623</v>
+      </c>
+      <c r="E23" t="n">
+        <v>15.99541</v>
+      </c>
+      <c r="F23" t="n">
+        <v>257.2547</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.61712</v>
+        <v>15.92392</v>
       </c>
       <c r="D24" t="n">
-        <v>1.12839</v>
+        <v>15.3198</v>
+      </c>
+      <c r="E24" t="n">
+        <v>15.6899</v>
+      </c>
+      <c r="F24" t="n">
+        <v>257.2745</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.61735</v>
+        <v>15.99564</v>
       </c>
       <c r="D25" t="n">
-        <v>1.13086</v>
+        <v>15.80328</v>
+      </c>
+      <c r="E25" t="n">
+        <v>15.8133</v>
+      </c>
+      <c r="F25" t="n">
+        <v>257.92388</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.61934</v>
+        <v>15.87715</v>
       </c>
       <c r="D26" t="n">
-        <v>1.11768</v>
+        <v>15.68885</v>
+      </c>
+      <c r="E26" t="n">
+        <v>15.81924</v>
+      </c>
+      <c r="F26" t="n">
+        <v>261.83399</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.6273300000000001</v>
+        <v>15.84807</v>
       </c>
       <c r="D27" t="n">
-        <v>1.11689</v>
+        <v>15.53077</v>
+      </c>
+      <c r="E27" t="n">
+        <v>15.58423</v>
+      </c>
+      <c r="F27" t="n">
+        <v>255.4017</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.60309</v>
+        <v>16.08708</v>
       </c>
       <c r="D28" t="n">
-        <v>1.13274</v>
+        <v>15.88493</v>
+      </c>
+      <c r="E28" t="n">
+        <v>15.89475</v>
+      </c>
+      <c r="F28" t="n">
+        <v>253.07533</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>15.94793</v>
+      </c>
+      <c r="D29" t="n">
+        <v>15.64651</v>
+      </c>
+      <c r="E29" t="n">
+        <v>15.76477</v>
+      </c>
+      <c r="F29" t="n">
+        <v>262.57264</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>0.6123499999999999</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1.11364</v>
+      <c r="C30" t="n">
+        <v>16.1536</v>
+      </c>
+      <c r="D30" t="n">
+        <v>15.77543</v>
+      </c>
+      <c r="E30" t="n">
+        <v>15.93582</v>
+      </c>
+      <c r="F30" t="n">
+        <v>255.95329</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Trace Pos 1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>16.76771</v>
+      </c>
+      <c r="D32" t="n">
+        <v>16.30979</v>
+      </c>
+      <c r="E32" t="n">
+        <v>16.67555</v>
+      </c>
+      <c r="F32" t="n">
+        <v>22.17464</v>
+      </c>
+      <c r="G32" t="n">
+        <v>34.79155</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>17.02833</v>
+      </c>
+      <c r="D33" t="n">
+        <v>16.0291</v>
+      </c>
+      <c r="E33" t="n">
+        <v>16.31434</v>
+      </c>
+      <c r="F33" t="n">
+        <v>22.06888</v>
+      </c>
+      <c r="G33" t="n">
+        <v>34.3731</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>16.7267</v>
+      </c>
+      <c r="D34" t="n">
+        <v>16.36757</v>
+      </c>
+      <c r="E34" t="n">
+        <v>16.53411</v>
+      </c>
+      <c r="F34" t="n">
+        <v>21.96684</v>
+      </c>
+      <c r="G34" t="n">
+        <v>34.7183</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>16.97141</v>
+      </c>
+      <c r="D35" t="n">
+        <v>15.90056</v>
+      </c>
+      <c r="E35" t="n">
+        <v>16.90236</v>
+      </c>
+      <c r="F35" t="n">
+        <v>21.99888</v>
+      </c>
+      <c r="G35" t="n">
+        <v>35.0183</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>16.43399</v>
+      </c>
+      <c r="D36" t="n">
+        <v>16.12801</v>
+      </c>
+      <c r="E36" t="n">
+        <v>16.35306</v>
+      </c>
+      <c r="F36" t="n">
+        <v>21.96959</v>
+      </c>
+      <c r="G36" t="n">
+        <v>34.29873</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>17.4874</v>
+      </c>
+      <c r="D37" t="n">
+        <v>16.46426</v>
+      </c>
+      <c r="E37" t="n">
+        <v>16.611</v>
+      </c>
+      <c r="F37" t="n">
+        <v>21.98281</v>
+      </c>
+      <c r="G37" t="n">
+        <v>34.7706</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>16.88366</v>
+      </c>
+      <c r="D38" t="n">
+        <v>16.38983</v>
+      </c>
+      <c r="E38" t="n">
+        <v>16.7203</v>
+      </c>
+      <c r="F38" t="n">
+        <v>21.89358</v>
+      </c>
+      <c r="G38" t="n">
+        <v>34.79581</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>16.64124</v>
+      </c>
+      <c r="D39" t="n">
+        <v>16.37009</v>
+      </c>
+      <c r="E39" t="n">
+        <v>16.6371</v>
+      </c>
+      <c r="F39" t="n">
+        <v>22.20676</v>
+      </c>
+      <c r="G39" t="n">
+        <v>34.26177</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>16.90511</v>
+      </c>
+      <c r="D40" t="n">
+        <v>16.04912</v>
+      </c>
+      <c r="E40" t="n">
+        <v>16.40591</v>
+      </c>
+      <c r="F40" t="n">
+        <v>22.10882</v>
+      </c>
+      <c r="G40" t="n">
+        <v>34.46319</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Via Pos 1</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.61978</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.10178</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.61266</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.13719</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.61874</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1.12725</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.6036899999999999</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1.13447</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.6049600000000001</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1.14245</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.61146</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1.11578</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.6064000000000001</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1.1152</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.61724</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.12426</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.6212</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1.12937</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Landing Pad 1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>17.24511</v>
+      </c>
+      <c r="D52" t="n">
+        <v>16.80645</v>
+      </c>
+      <c r="E52" t="n">
+        <v>16.90768</v>
+      </c>
+      <c r="F52" t="n">
+        <v>42.36985</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>16.88013</v>
+      </c>
+      <c r="D53" t="n">
+        <v>16.59379</v>
+      </c>
+      <c r="E53" t="n">
+        <v>16.7825</v>
+      </c>
+      <c r="F53" t="n">
+        <v>42.57409</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>17.16862</v>
+      </c>
+      <c r="D54" t="n">
+        <v>16.66038</v>
+      </c>
+      <c r="E54" t="n">
+        <v>16.89079</v>
+      </c>
+      <c r="F54" t="n">
+        <v>43.06284</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>17.09996</v>
+      </c>
+      <c r="D55" t="n">
+        <v>16.63022</v>
+      </c>
+      <c r="E55" t="n">
+        <v>16.69452</v>
+      </c>
+      <c r="F55" t="n">
+        <v>42.92667</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>16.94042</v>
+      </c>
+      <c r="D56" t="n">
+        <v>16.48609</v>
+      </c>
+      <c r="E56" t="n">
+        <v>16.89164</v>
+      </c>
+      <c r="F56" t="n">
+        <v>42.03572</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>16.94295</v>
+      </c>
+      <c r="D57" t="n">
+        <v>16.61098</v>
+      </c>
+      <c r="E57" t="n">
+        <v>16.75656</v>
+      </c>
+      <c r="F57" t="n">
+        <v>43.03072</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>16.94231</v>
+      </c>
+      <c r="D58" t="n">
+        <v>16.7267</v>
+      </c>
+      <c r="E58" t="n">
+        <v>16.75579</v>
+      </c>
+      <c r="F58" t="n">
+        <v>42.87209</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>17.0526</v>
+      </c>
+      <c r="D59" t="n">
+        <v>16.44619</v>
+      </c>
+      <c r="E59" t="n">
+        <v>16.69402</v>
+      </c>
+      <c r="F59" t="n">
+        <v>43.6505</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>17.17393</v>
+      </c>
+      <c r="D60" t="n">
+        <v>16.7263</v>
+      </c>
+      <c r="E60" t="n">
+        <v>17.01488</v>
+      </c>
+      <c r="F60" t="n">
+        <v>43.45707</v>
       </c>
     </row>
   </sheetData>
